--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 8:51:53 am</t>
+    <t>28/7/2026, 10:34:36 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:34:36 am</t>
+    <t>28/7/2026, 10:42:41 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:42:41 am</t>
+    <t>28/7/2026, 10:47:44 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:47:44 am</t>
+    <t>28/7/2026, 10:59:40 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:59:40 am</t>
+    <t>28/7/2026, 11:08:31 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:08:31 am</t>
+    <t>28/7/2026, 11:12:57 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:12:57 am</t>
+    <t>28/7/2026, 11:17:41 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:17:41 am</t>
+    <t>28/7/2026, 11:28:01 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:28:01 am</t>
+    <t>28/7/2026, 11:31:48 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:31:48 am</t>
+    <t>28/7/2026, 11:38:00 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:38:00 am</t>
+    <t>28/7/2026, 11:40:43 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:40:43 am</t>
+    <t>28/7/2026, 11:43:45 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>

--- a/load-tests/reports/Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/Baseline_Load_Test_Report.xlsx
@@ -49,7 +49,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:43:45 am</t>
+    <t>28/7/2026, 11:57:30 am</t>
   </si>
   <si>
     <t>Baseline Load Test Performance Metrics</t>
